--- a/dist/SUBMISSION_FINAL/P4_Singapore_JABES/p4_singapore_mir_replication_data.xlsx
+++ b/dist/SUBMISSION_FINAL/P4_Singapore_JABES/p4_singapore_mir_replication_data.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Regression_Coefficients" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Turning_Points" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Robustness" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Figures_Embedded" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +49,25 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00305496"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -80,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,6 +111,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -165,6 +191,86 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3943350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3676650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3781425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,7 +696,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1360,7 +1465,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2546,7 +2650,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2755,4 +2858,95 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>P4_Singapore_JABES — Embedded Figures (data-driven, source-traceable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Each figure below was rendered from a CSV / data file produced by the paper's Stata or R replication pipeline. Provenance is listed under each figure. See 'STATA_REPLICATION_GUIDE.md' (Vietnamese + English) for end-to-end reproduction instructions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Figure 1: figure_1_conceptual_model.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: scripts/render_conceptual_models.py → matplotlib (theoretical diagram, not data-driven)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Figure 2: figure_2_dai_marginal_effect.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: p4/replication/figures/ ← p4/replication/dai_marginal_effects.csv (Stata margins)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Figure 3: figure_3_predicted_ip_curve.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: p4/replication/figures/ ← p4/replication/predicted_curve.csv (Stata predict post-estimation)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A37:H37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>